--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_118_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_118_R12.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0588</v>
+        <v>3.1961</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3489</v>
+        <v>5.0847</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2901</v>
+        <v>-1.8887</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8671</v>
+        <v>2.1736</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9072</v>
+        <v>5.4594</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0401</v>
+        <v>-3.2858</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8608</v>
+        <v>5.79</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1615</v>
+        <v>5.5995</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6993</v>
+        <v>0.1904</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9937</v>
+        <v>-3.6164</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2543</v>
+        <v>-0.1401</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-3.4762</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1041</v>
+        <v>-0.3539</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6563</v>
+        <v>-0.44</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7604</v>
+        <v>0.0861</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5361</v>
+        <v>1.6083</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1444</v>
+        <v>2.2862</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.6805</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6063</v>
+        <v>3.0087</v>
       </c>
       <c r="E3" t="n">
-        <v>4.495</v>
+        <v>4.4668</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8887</v>
+        <v>-1.4581</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1736</v>
+        <v>1.8671</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4594</v>
+        <v>1.9072</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.2858</v>
+        <v>-0.0401</v>
       </c>
       <c r="J3" t="n">
-        <v>5.79</v>
+        <v>2.8608</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5995</v>
+        <v>2.1615</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1904</v>
+        <v>0.6993</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.6164</v>
+        <v>-0.9937</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1401</v>
+        <v>-0.2543</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.4762</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9436</v>
+        <v>0.054</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0297</v>
+        <v>-0.5384</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0861</v>
+        <v>0.5924</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6083</v>
+        <v>-0.5361</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2862</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6291</v>
+        <v>1.2518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8766</v>
+        <v>1.2305</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2476</v>
+        <v>0.0213</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5272</v>
@@ -766,13 +766,13 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.434</v>
+        <v>0.1887</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6563</v>
+        <v>-0.3025</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2223</v>
+        <v>0.4911</v>
       </c>
       <c r="V4" t="n">
         <v>2.2862</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>M. BOSNJAKOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5184</v>
+        <v>-0.9246</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4068</v>
+        <v>-0.2362</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8884</v>
+        <v>-0.6884</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5708</v>
+        <v>-0.73</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5343</v>
+        <v>0.1801</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.1051</v>
+        <v>-0.9101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.317</v>
+        <v>0.0704</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3143</v>
+        <v>0.0336</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9973</v>
+        <v>0.0368</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8878</v>
+        <v>-0.8004</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.78</v>
+        <v>0.1465</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1078</v>
+        <v>-0.9469</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3237</v>
+        <v>0.0373</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3397</v>
+        <v>-0.0747</v>
       </c>
       <c r="U5" t="n">
-        <v>0.984</v>
+        <v>0.112</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BOSNJAKOVIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9918</v>
+        <v>-1.0498</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2362</v>
+        <v>-0.3257</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7556</v>
+        <v>-0.724</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.73</v>
+        <v>-1.2194</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1801</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9101</v>
+        <v>-1.2112</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0704</v>
+        <v>0.0672</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0336</v>
+        <v>0.0672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8004</v>
+        <v>-1.2866</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1465</v>
+        <v>-0.0755</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9469</v>
+        <v>-1.2112</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0299</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0747</v>
+        <v>-0.393</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0448</v>
+        <v>-0.293</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6053</v>
+        <v>-1.6377</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6796</v>
+        <v>-0.4804</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9257</v>
+        <v>-1.1573</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2194</v>
+        <v>-2.5708</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.5343</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2112</v>
+        <v>-3.1051</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0672</v>
+        <v>0.317</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0672</v>
+        <v>1.3143</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.9973</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2866</v>
+        <v>-2.8878</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0755</v>
+        <v>-0.78</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2112</v>
+        <v>-2.1078</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2415</v>
+        <v>1.1677</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7468</v>
+        <v>0.4525</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4946</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0001</v>
+        <v>-1.697</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4235</v>
+        <v>-1.1876</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5766</v>
+        <v>-0.5094</v>
       </c>
       <c r="G9" t="n">
         <v>-2.599</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.883</v>
+        <v>-0.5799</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0297</v>
+        <v>-0.7938</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1467</v>
+        <v>0.2139</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2649</v>
+        <v>-2.4672</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2109</v>
+        <v>-0.4468</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0539</v>
+        <v>-2.0203</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9757</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4942</v>
+        <v>0.2919</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2306</v>
+        <v>0.2642</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7586</v>
+        <v>-2.5728</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2956</v>
+        <v>-1.9418</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.463</v>
+        <v>-0.631</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7083</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8158</v>
+        <v>-0.63</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8215</v>
+        <v>-0.4676</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0057</v>
+        <v>-0.1623</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3371</v>
+        <v>-3.2528</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7537</v>
+        <v>-1.6358</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5834</v>
+        <v>-1.617</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9255</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.7912</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2781</v>
+        <v>-0.3117</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5047</v>
+        <v>-7.504799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>4.469900000000001</v>
+        <v>4.4698</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.9747</v>
+        <v>-11.9746</v>
       </c>
       <c r="G13" t="n">
         <v>-9.734499999999999</v>
@@ -1441,7 +1441,7 @@
         <v>-13.1494</v>
       </c>
       <c r="J13" t="n">
-        <v>8.5631</v>
+        <v>8.563100000000002</v>
       </c>
       <c r="K13" t="n">
         <v>5.1175</v>
@@ -1459,7 +1459,7 @@
         <v>-16.5949</v>
       </c>
       <c r="P13" t="n">
-        <v>3.479299999999999</v>
+        <v>3.4793</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.438</v>
@@ -1468,10 +1468,10 @@
         <v>13.9173</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5333</v>
+        <v>-1.5334</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0839</v>
+        <v>-3.084</v>
       </c>
       <c r="U13" t="n">
         <v>1.5506</v>
@@ -1483,7 +1483,7 @@
         <v>9.428399999999998</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.144800000000002</v>
+        <v>-9.1448</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5499</v>
+        <v>3.8752</v>
       </c>
       <c r="E14" t="n">
         <v>4.3946</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8447</v>
+        <v>-0.5194</v>
       </c>
       <c r="G14" t="n">
         <v>2.0382</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6506</v>
+        <v>-0.3253</v>
       </c>
       <c r="T14" t="n">
         <v>-0.6642</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0136</v>
+        <v>0.3389</v>
       </c>
       <c r="V14" t="n">
         <v>1.4665</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.244</v>
+        <v>2.8169</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6851</v>
+        <v>3.4032</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5589</v>
+        <v>-0.5863</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9474</v>
+        <v>1.823</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6183</v>
+        <v>-1.2987</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3292</v>
+        <v>3.1218</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5652</v>
+        <v>3.9108</v>
       </c>
       <c r="K15" t="n">
-        <v>0.39</v>
+        <v>-0.1611</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1752</v>
+        <v>4.0719</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3823</v>
+        <v>-2.0878</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2283</v>
+        <v>-1.1377</v>
       </c>
       <c r="O15" t="n">
-        <v>0.154</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.227</v>
+        <v>-0.2201</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8338</v>
+        <v>-0.5619</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3932</v>
+        <v>0.3418</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4665</v>
+        <v>1.214</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3943</v>
+        <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6039</v>
+        <v>2.6156</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6391</v>
+        <v>0.9774</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0352</v>
+        <v>1.6382</v>
       </c>
       <c r="G16" t="n">
-        <v>1.823</v>
+        <v>3.9474</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2987</v>
+        <v>0.6183</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1218</v>
+        <v>3.3292</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9108</v>
+        <v>3.5652</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1611</v>
+        <v>0.39</v>
       </c>
       <c r="L16" t="n">
-        <v>4.0719</v>
+        <v>3.1752</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0878</v>
+        <v>0.3823</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1377</v>
+        <v>0.2283</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9500999999999999</v>
+        <v>0.154</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4332</v>
+        <v>0.5985</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.326</v>
+        <v>0.1261</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1072</v>
+        <v>0.4725</v>
       </c>
       <c r="V16" t="n">
-        <v>1.214</v>
+        <v>-1.4665</v>
       </c>
       <c r="W16" t="n">
-        <v>1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0716</v>
+        <v>1.3354</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9735</v>
+        <v>1.8556</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9019</v>
+        <v>-0.5202</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3057</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3593</v>
+        <v>0.6231</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0193</v>
+        <v>-0.1373</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3787</v>
+        <v>0.7604</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.845</v>
+        <v>1.1316</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0624</v>
+        <v>2.4163</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2174</v>
+        <v>-1.2846</v>
       </c>
       <c r="G18" t="n">
         <v>1.4774</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.3872</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4463</v>
+        <v>0.3791</v>
       </c>
       <c r="V18" t="n">
         <v>3.7527</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1759</v>
+        <v>0.5884</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3377</v>
+        <v>-0.209</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1618</v>
+        <v>0.7975</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5962</v>
+        <v>0.6876</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.6842</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1372</v>
+        <v>0.0034</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8501</v>
+        <v>1.0382</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7765</v>
+        <v>0.9278</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0736</v>
+        <v>0.1104</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2539</v>
+        <v>-0.3505</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0431</v>
+        <v>-0.2435</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2108</v>
+        <v>-0.107</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0.42</v>
+        <v>0.9524</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4876</v>
+        <v>0.3068</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0677</v>
+        <v>0.6456</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-0.8197</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0349</v>
+        <v>0.3292</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7988</v>
+        <v>1.318</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7639</v>
+        <v>-0.9888</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6876</v>
+        <v>1.5557</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6842</v>
+        <v>-1.5426</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0034</v>
+        <v>3.0983</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0382</v>
+        <v>2.4029</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9278</v>
+        <v>-1.4348</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1104</v>
+        <v>3.8376</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3505</v>
+        <v>-0.8472</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2435</v>
+        <v>-0.1078</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.107</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.329</v>
+        <v>0.454</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2829</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6119</v>
+        <v>0.3791</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8197</v>
+        <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4254</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3506</v>
+        <v>-0.1614</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.8659</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0788</v>
+        <v>-1.0274</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5557</v>
+        <v>0.5962</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5426</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0983</v>
+        <v>-0.1372</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4029</v>
+        <v>0.8501</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4348</v>
+        <v>0.7765</v>
       </c>
       <c r="L21" t="n">
-        <v>3.8376</v>
+        <v>0.0736</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8472</v>
+        <v>-0.2539</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1078</v>
+        <v>-0.0431</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.2108</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2258</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5149</v>
+        <v>0.0158</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2891</v>
+        <v>0.0668</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9256</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="E22" t="n">
         <v>-2.9107</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9851</v>
+        <v>2.0644</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0596</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0618</v>
+        <v>1.1411</v>
       </c>
       <c r="T22" t="n">
         <v>0.3541</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7077</v>
+        <v>0.787</v>
       </c>
       <c r="V22" t="n">
         <v>0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6744</v>
+        <v>-2.6072</v>
       </c>
       <c r="E23" t="n">
         <v>-0.1367</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5377</v>
+        <v>-2.4705</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0259</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4182</v>
+        <v>0.4854</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6083</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.504800000000001</v>
+        <v>9.077400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>11.9745</v>
+        <v>11.9746</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.4696</v>
+        <v>-2.8971</v>
       </c>
       <c r="G24" t="n">
         <v>9.734300000000001</v>
@@ -2326,13 +2326,13 @@
         <v>10.438</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5331</v>
+        <v>3.1058</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5507</v>
+        <v>-1.5508</v>
       </c>
       <c r="U24" t="n">
-        <v>3.0838</v>
+        <v>4.6566</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2836000000000003</v>
